--- a/human_resources_forms/018_objective_setting_confirmation_form--human_resources_forms.xlsx
+++ b/human_resources_forms/018_objective_setting_confirmation_form--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1079,8 +1079,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'confirm'}</t>
+          <t>confirm</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Confirm'}</t>
+          <t>Confirm</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'do_not_confirm'}</t>
+          <t>do_not_confirm</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Do not confirm'}</t>
+          <t>Do not confirm</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'confirmed'}</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Confirmed'}</t>
+          <t>Confirmed</t>
         </is>
       </c>
     </row>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'not_confirmed'}</t>
+          <t>not_confirmed</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Not Confirmed'}</t>
+          <t>Not Confirmed</t>
         </is>
       </c>
     </row>
